--- a/out/Attention-Mamba1_repeat_1_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.614362084491469</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.614362084491469</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.614362084491469</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.614362084491469</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.614362084491469</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.614362084491469</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.614362084491469</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.847209366080289</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001010952256203163</v>
+        <v>-0.0002713679539981531</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.165478643326382</v>
+        <v>3.128471649169196</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.332758906302877</v>
+        <v>6.261779502472098</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1747686988151495</v>
+        <v>0.4691282792029723</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.515253473380528</v>
+        <v>4.067365466341003</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2185177963166227</v>
+        <v>0.5865629934741532</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.777548076313308</v>
+        <v>4.771437743131623</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3132442247207192</v>
+        <v>0.8408354321028069</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.01436208449146897</v>
+        <v>2.247209366080289</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.18564204870236</v>
+        <v>5.866876523904789</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.335109273102467</v>
+        <v>0.8995273598483454</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.542639725112905</v>
+        <v>6.825158502677066</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3551482850863055</v>
+        <v>0.953317693302591</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.917852379898281</v>
+        <v>7.832334596659926</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1602718157365199</v>
+        <v>0.4302138785838083</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.882952599471112</v>
+        <v>7.738653790044861</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0774033183678887</v>
+        <v>0.2077736397675611</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.877363032767741</v>
+        <v>7.723649799060822</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0368803767588179</v>
+        <v>0.09899856642976733</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.873658938326831</v>
+        <v>7.713707003730934</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01092610414842192</v>
+        <v>0.02933222147848974</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.858591915619327</v>
+        <v>7.673268155022284</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007225508188716778</v>
+        <v>0.01940265117200891</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.86211226318165</v>
+        <v>7.682725193563676</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003695655196673187</v>
+        <v>0.00992802691050673</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.862273765165457</v>
+        <v>7.68316712869535</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001887524818425262</v>
+        <v>0.005076630469899322</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.862351965467743</v>
+        <v>7.683385469314069</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000706471822152007</v>
+        <v>0.001905377530969857</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.861875700426862</v>
+        <v>7.682115744028911</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003827528093115432</v>
+        <v>0.001036157543300356</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.86193440608516</v>
+        <v>7.682281617366588</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001817615383812072</v>
+        <v>0.0004964745988023053</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.861914900855136</v>
+        <v>7.682237750672888</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001111067038573348</v>
+        <v>0.0003049458619920377</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.86195447029126</v>
+        <v>7.682351917857422</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.573278029164164e-05</v>
+        <v>0.0001576403268827014</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.861954761689057</v>
+        <v>7.682361088041354</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.397370079277015e-05</v>
+        <v>7.392835733202904e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.861947937989843</v>
+        <v>7.682351202608311</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.418719566644068e-05</v>
+        <v>4.488670873274575e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.861951326392446</v>
+        <v>7.682368292844795</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>3.15927894345679e-06</v>
+        <v>1.831222555273368e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.861944611406574</v>
+        <v>7.682358717660893</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-8.825233700581938e-07</v>
+        <v>5.293691574854516e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.861938515150132</v>
+        <v>7.682350977019786</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>5.63141154556023e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.861933845881495</v>
+        <v>7.682346803848194</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.031182895915095e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.861928556733933</v>
+        <v>7.682341081569163</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.861928533999631</v>
+        <v>7.682336012213795</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>-3.735991635587426e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.861928852279848</v>
+        <v>7.682331647239827</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.861929943526305</v>
+        <v>7.682332738486283</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.861929253919169</v>
+        <v>7.682332048879147</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.861929284231571</v>
+        <v>7.682332079191549</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.861929094779061</v>
+        <v>7.682331889739038</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.861929147825764</v>
+        <v>7.682331942785741</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.861929200872467</v>
+        <v>7.682331995832444</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.861929162981964</v>
+        <v>7.682331957941942</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.861929034154258</v>
+        <v>7.682331829114236</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.86192889017035</v>
+        <v>7.682331685130328</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.861928731030241</v>
+        <v>7.68233152599022</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.861928784076945</v>
+        <v>7.682331579036923</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.861928731030241</v>
+        <v>7.68233152599022</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.861928731030241</v>
+        <v>7.68233152599022</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.861928549155832</v>
+        <v>7.68233134411581</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.614362084491469</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.861928715874041</v>
+        <v>7.68233151083402</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.861928912904651</v>
+        <v>7.682331707864629</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.861928753764543</v>
+        <v>7.682331548724521</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.861928791655045</v>
+        <v>7.682331586615022</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.861928988685655</v>
+        <v>7.682331783645633</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.861928965951354</v>
+        <v>7.682331760911333</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.861928814389346</v>
+        <v>7.682331609349323</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.861928738608342</v>
+        <v>7.682331533568321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.861928837123648</v>
+        <v>7.682331632083625</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.861928844701748</v>
+        <v>7.682331639661726</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.861929109935262</v>
+        <v>7.682331904895238</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.861928814389346</v>
+        <v>7.682331609349323</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.861929056888559</v>
+        <v>7.682331851848537</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.861929140247663</v>
+        <v>7.682331935207641</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.861928973529454</v>
+        <v>7.682331768489432</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.861929162981964</v>
+        <v>7.682331957941942</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.861928814389346</v>
+        <v>7.682331609349323</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.861928609780636</v>
+        <v>7.682331404740613</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.861928723452142</v>
+        <v>7.682331518412119</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.861928738608342</v>
+        <v>7.682331533568321</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.86192850368723</v>
+        <v>7.682331298647208</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.861928564312033</v>
+        <v>7.682331359272011</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.861928435484327</v>
+        <v>7.682331230444305</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.861928571890133</v>
+        <v>7.682331366850112</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.861928746186443</v>
+        <v>7.68233154114642</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.86192889017035</v>
+        <v>7.682331685130328</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.861928723452142</v>
+        <v>7.682331518412119</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.861928715874041</v>
+        <v>7.68233151083402</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.861928427906226</v>
+        <v>7.682331222866203</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.861928443062427</v>
+        <v>7.682331238022404</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.861928670405439</v>
+        <v>7.682331465365417</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.861928655249238</v>
+        <v>7.682331450209215</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.861928761342643</v>
+        <v>7.682331556302622</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.861928488531029</v>
+        <v>7.682331283491006</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.861928587046334</v>
+        <v>7.682331382006311</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.861928738608342</v>
+        <v>7.682331533568321</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.861928753764543</v>
+        <v>7.682331548724521</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.861928731030241</v>
+        <v>7.68233152599022</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.861928814389346</v>
+        <v>7.682331609349323</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.861928912904651</v>
+        <v>7.682331707864629</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.861928746186443</v>
+        <v>7.68233154114642</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.861928731030241</v>
+        <v>7.68233152599022</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.86192870071784</v>
+        <v>7.682331495677817</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.861928685561639</v>
+        <v>7.682331480521618</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.861928723452142</v>
+        <v>7.682331518412119</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.861928738608342</v>
+        <v>7.682331533568321</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.01436208449146897</v>
+        <v>-1.069469496003421</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.861928731030241</v>
+        <v>7.68233152599022</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001010952256203163</v>
+        <v>-0.0001133880712013924</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.165478643326382</v>
+        <v>1.307196921849627</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.332758906302877</v>
+        <v>2.616414685787688</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.1747686988151495</v>
+        <v>0.196020032233863</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.515253473380528</v>
+        <v>1.699503238813676</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2185177963166227</v>
+        <v>0.2450887643454178</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.777548076313308</v>
+        <v>1.993691978195196</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3132442247207192</v>
+        <v>0.3513335813797941</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.18564204870236</v>
+        <v>2.451408903233726</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.335109273102467</v>
+        <v>0.3758573399960973</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.542639725112905</v>
+        <v>2.851816567973342</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3551482850863055</v>
+        <v>0.3983330228402793</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC45" t="n">
-        <v>2.917852379898281</v>
+        <v>3.272654495323176</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1602718157365199</v>
+        <v>0.1797602847016814</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.01436208449146897</v>
+        <v>-0.8562916185181857</v>
       </c>
       <c r="JC46" t="n">
-        <v>2.882952599471112</v>
+        <v>3.233510884742948</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0774033183678887</v>
+        <v>0.08681664445251344</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-6.534848009080795</v>
+        <v>-0.8562916185181857</v>
       </c>
       <c r="JC47" t="n">
-        <v>2.877363032767741</v>
+        <v>3.22724159955039</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0368803767588179</v>
+        <v>0.0413655463855841</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.01436208449146897</v>
+        <v>-0.8562916185181857</v>
       </c>
       <c r="JC48" t="n">
-        <v>2.873658938326831</v>
+        <v>3.223087103417231</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01092610414842192</v>
+        <v>0.0122550718091148</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.858591915619327</v>
+        <v>3.206188889568274</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007225508188716778</v>
+        <v>0.008104088949749367</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.614362084491469</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.86211226318165</v>
+        <v>3.210137837868243</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.003695655196673187</v>
+        <v>0.004145322685341</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.862273765165457</v>
+        <v>3.210319594281804</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001887524818425262</v>
+        <v>0.002118050447903658</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.862351965467743</v>
+        <v>3.210407926319766</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000706471822152007</v>
+        <v>0.0007935135876280504</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.861875700426862</v>
+        <v>3.209874287185122</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003827528093115432</v>
+        <v>0.0004297781500152835</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.86193440608516</v>
+        <v>3.209940710577373</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001817615383812072</v>
+        <v>0.0002048087069473987</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.861914900855136</v>
+        <v>3.20991944939332</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001111067038573348</v>
+        <v>0.0001248820755014253</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.86195447029126</v>
+        <v>3.209964306728644</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.573278029164164e-05</v>
+        <v>6.29383643940398e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.861954761689057</v>
+        <v>3.209965225919401</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>2.397370079277015e-05</v>
+        <v>2.797007331591087e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.861947937989843</v>
+        <v>3.20995818516889</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.418719566644068e-05</v>
+        <v>1.546634204420339e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.861951326392446</v>
+        <v>3.209962413188048</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>3.15927894345679e-06</v>
+        <v>4.324890221093473e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.861944611406574</v>
+        <v>3.20995546944298</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.861938515150132</v>
+        <v>3.209949236780731</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.861933845881495</v>
+        <v>3.209944650871199</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.861928556733933</v>
+        <v>3.20993921773973</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>-4.053889915940302e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.861928533999631</v>
+        <v>3.209934171118663</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.861928852279848</v>
+        <v>3.209934489398879</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.01436208449146897</v>
+        <v>-0.8562916185181857</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.861929943526305</v>
+        <v>3.209935580645336</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.888145809259093</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.861929253919169</v>
+        <v>3.2099348910382</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-6.534848009080795</v>
+        <v>-2.92</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.861929284231571</v>
+        <v>3.209934921350602</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-6.534848009080795</v>
+        <v>-2.92</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.861929094779061</v>
+        <v>3.209934731898092</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-6.534848009080795</v>
+        <v>-2.92</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.861929147825764</v>
+        <v>3.209934784944795</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-6.534848009080795</v>
+        <v>-1.888145809259093</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.861929200872467</v>
+        <v>3.209934837991498</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.01436208449146897</v>
+        <v>-0.8562916185181857</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.861929162981964</v>
+        <v>3.209934800100995</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.861929034154258</v>
+        <v>3.209934671273288</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.86192889017035</v>
+        <v>3.209934527289381</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.861928731030241</v>
+        <v>3.209934368149273</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.861928784076945</v>
+        <v>3.209934421195975</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.861928731030241</v>
+        <v>3.209934368149273</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.861928731030241</v>
+        <v>3.209934368149273</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.861928549155832</v>
+        <v>3.209934186274864</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.614362084491469</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.861928715874041</v>
+        <v>3.209934352993072</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.3755625722227216</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.861928912904651</v>
+        <v>3.209934550023682</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.861928753764543</v>
+        <v>3.209934390883574</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.861928791655045</v>
+        <v>3.209934428774075</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.861928988685655</v>
+        <v>3.209934625804686</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.861928965951354</v>
+        <v>3.209934603070385</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.861928814389346</v>
+        <v>3.209934451508377</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.861928738608342</v>
+        <v>3.209934375727373</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.861928837123648</v>
+        <v>3.209934474242679</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.861928844701748</v>
+        <v>3.209934481820779</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.861929109935262</v>
+        <v>3.209934747054293</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.861928814389346</v>
+        <v>3.209934451508377</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.861929056888559</v>
+        <v>3.20993469400759</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.861929140247663</v>
+        <v>3.209934777366694</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.861928973529454</v>
+        <v>3.209934610648486</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.861929162981964</v>
+        <v>3.209934800100995</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.861928814389346</v>
+        <v>3.209934451508377</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.861928609780636</v>
+        <v>3.209934246899666</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.861928723452142</v>
+        <v>3.209934360571172</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.861928738608342</v>
+        <v>3.209934375727373</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.86192850368723</v>
+        <v>3.209934140806261</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.861928564312033</v>
+        <v>3.209934201431064</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.861928435484327</v>
+        <v>3.209934072603357</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.861928571890133</v>
+        <v>3.209934209009165</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.861928746186443</v>
+        <v>3.209934383305473</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.86192889017035</v>
+        <v>3.209934527289381</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.861928723452142</v>
+        <v>3.209934360571172</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.861928715874041</v>
+        <v>3.209934352993072</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.861928427906226</v>
+        <v>3.209934065025257</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.861928443062427</v>
+        <v>3.209934080181458</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.861928670405439</v>
+        <v>3.20993430752447</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.861928655249238</v>
+        <v>3.209934292368269</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.861928761342643</v>
+        <v>3.209934398461674</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.861928488531029</v>
+        <v>3.20993412565006</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.861928587046334</v>
+        <v>3.209934224165365</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.861928738608342</v>
+        <v>3.209934375727373</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.861928753764543</v>
+        <v>3.209934390883574</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.861928731030241</v>
+        <v>3.209934368149273</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.861928814389346</v>
+        <v>3.209934451508377</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.861928912904651</v>
+        <v>3.209934550023682</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.861928746186443</v>
+        <v>3.209934383305473</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.861928731030241</v>
+        <v>3.209934368149273</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.86192870071784</v>
+        <v>3.209934337836871</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.861928685561639</v>
+        <v>3.209934322680671</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.861928723452142</v>
+        <v>3.209934360571172</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.861928738608342</v>
+        <v>3.209934375727373</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.01436208449146897</v>
+        <v>0.1755625722227216</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.861928731030241</v>
+        <v>3.209934368149273</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.003990591503679752</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1599999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.004284373484551907</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.01999999999999991</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.004108828492462635</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.3755625722227216</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.007315183989703655</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.3755625722227216</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.005404793657362461</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.3755625722227216</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0047961650416255</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.3755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.004489299841225147</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.3755625722227216</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.00481883343309164</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.3755625722227216</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.004850310273468494</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.3755625722227216</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.004848829470574856</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.004796112887561321</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.004667091183364391</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.005218899808824062</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004997228272259235</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.005640235729515553</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.005384205840528011</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.005609533749520779</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.005334624089300632</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.005947175435721874</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.006026570685207844</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.006300834007561207</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.007168627344071865</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.005295452661812305</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.005055048502981663</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.004908098839223385</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.004728215746581554</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.004546920768916607</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.005342043004930019</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.00474464800208807</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.004617695696651936</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.004413398914039135</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.004430235363543034</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.004700659774243832</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.004757883958518505</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.006342954002320766</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01323719788342714</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.005814737640321255</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.005190092138946056</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001133880712013924</v>
+        <v>-0.0001122012974235695</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.307196921849627</v>
+        <v>1.293515172944791</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.004678425379097462</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.616414685787688</v>
+        <v>2.589030038463338</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.196020032233863</v>
+        <v>0.1939683702640152</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004536076448857784</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.699503238813676</v>
+        <v>1.681715424668078</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2450887643454178</v>
+        <v>0.2425236327967858</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003945988602936268</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>1.993691978195196</v>
+        <v>1.97282507815404</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3513335813797941</v>
+        <v>0.3476564774697143</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.006718714721500874</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.16</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.451408903233726</v>
+        <v>2.425751267116964</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.3758573399960973</v>
+        <v>0.3719235671722639</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.007770820520818233</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>2.851816567973342</v>
+        <v>2.821967844633815</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3983330228402793</v>
+        <v>0.3941632787890039</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.009559034369885921</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.272654495323176</v>
+        <v>3.238400455103479</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1797602847016814</v>
+        <v>0.1778785567634709</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01067945081740618</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.8562916185181857</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.233510884742948</v>
+        <v>3.199666597738845</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.08681664445251344</v>
+        <v>0.08590721270315163</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.001520373858511448</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.8562916185181857</v>
+        <v>0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.22724159955039</v>
+        <v>3.193462939818619</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.0413655463855841</v>
+        <v>0.0409328421280688</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.003825013525784016</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8562916185181857</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.223087103417231</v>
+        <v>3.189351901788198</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0122550718091148</v>
+        <v>0.01212646203549936</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0009698392823338509</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.206188889568274</v>
+        <v>3.172630399830561</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.008104088949749367</v>
+        <v>0.0080194991171773</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.002762214280664921</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.210137837868243</v>
+        <v>3.176538105032221</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.004145322685341</v>
+        <v>0.004102028660173859</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.001154757104814053</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.210319594281804</v>
+        <v>3.176717913536373</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002118050447903658</v>
+        <v>0.002095903880879533</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.002791755832731724</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.210407926319766</v>
+        <v>3.176805272219816</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007935135876280504</v>
+        <v>0.0007851878535390375</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.002511917613446712</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.209874287185122</v>
+        <v>3.176277144962405</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004297781500152835</v>
+        <v>0.0004256531201289904</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001991207711398602</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.209940710577373</v>
+        <v>3.176342823157545</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002048087069473987</v>
+        <v>0.0002024245170957237</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.001991298981010914</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.20991944939332</v>
+        <v>3.176321746759676</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001248820755014253</v>
+        <v>0.0001229141652665552</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.002091548405587673</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.209964306728644</v>
+        <v>3.176366038133338</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>6.29383643940398e-05</v>
+        <v>6.190899523655436e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.001099447719752789</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.209965225919401</v>
+        <v>3.176366913107989</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01789640262722969</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.20995818516889</v>
+        <v>3.176359872357477</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.002635910175740719</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.209962413188048</v>
+        <v>3.176364100376635</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.0002836054190993309</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.20995546944298</v>
+        <v>3.176357156631568</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.001059277914464474</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.209949236780731</v>
+        <v>3.176350923969319</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001585361547768116</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.209944650871199</v>
+        <v>3.176346338059786</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.00221563596278429</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.20993921773973</v>
+        <v>3.176340904928317</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.004041283391416073</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.209934171118663</v>
+        <v>3.176335858307249</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01334490161389112</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.209934489398879</v>
+        <v>3.176336176587465</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.04927634820342064</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8562916185181857</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.209935580645336</v>
+        <v>3.176337267833922</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.005197684280574322</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.888145809259093</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.2099348910382</v>
+        <v>3.176336578226787</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.006580931134521961</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.92</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.209934921350602</v>
+        <v>3.176336608539188</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003174777142703533</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.92</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.209934731898092</v>
+        <v>3.176336419086678</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0003487290814518929</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.92</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.209934784944795</v>
+        <v>3.176336472133381</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0001447601243853569</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.888145809259093</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.209934837991498</v>
+        <v>3.176336525180084</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.0004219124093651772</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8562916185181857</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.209934800100995</v>
+        <v>3.176336487289582</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.001027452759444714</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.209934671273288</v>
+        <v>3.176336358461875</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.001288971863687038</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.209934527289381</v>
+        <v>3.176336214477967</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.001307575963437557</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.209934368149273</v>
+        <v>3.176336055337859</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.001174743287265301</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.209934421195975</v>
+        <v>3.176336108384562</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.000516415573656559</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.209934368149273</v>
+        <v>3.176336055337859</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.001243737526237965</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.209934368149273</v>
+        <v>3.176336055337859</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.002239192835986614</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.209934186274864</v>
+        <v>3.176335873463449</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.002243299968540668</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.209934352993072</v>
+        <v>3.176336040181658</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0006087804213166237</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.209934550023682</v>
+        <v>3.176336237212269</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0005947249010205269</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.209934390883574</v>
+        <v>3.17633607807216</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.001979992724955082</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.209934428774075</v>
+        <v>3.176336115962662</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.002702820114791393</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.209934625804686</v>
+        <v>3.176336312993273</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0006689475849270821</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.209934603070385</v>
+        <v>3.176336290258972</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0005878666415810585</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.209934451508377</v>
+        <v>3.176336138696963</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0008665574714541435</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.209934375727373</v>
+        <v>3.17633606291596</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001073666848242283</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.209934474242679</v>
+        <v>3.176336161431264</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.002684065140783787</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.209934481820779</v>
+        <v>3.176336169009365</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.001199589110910892</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.209934747054293</v>
+        <v>3.176336434242879</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0008982056751847267</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.209934451508377</v>
+        <v>3.176336138696963</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.001836971379816532</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.20993469400759</v>
+        <v>3.176336381196176</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.000426863320171833</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.209934777366694</v>
+        <v>3.17633646455528</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.006517895497381687</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.209934610648486</v>
+        <v>3.176336297837071</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0006118053570389748</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.209934800100995</v>
+        <v>3.176336487289582</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0008507268503308296</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.209934451508377</v>
+        <v>3.176336138696963</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.0006534485146403313</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.209934246899666</v>
+        <v>3.176335934088253</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0008183671161532402</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.209934360571172</v>
+        <v>3.176336047759759</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.00131609383970499</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.209934375727373</v>
+        <v>3.17633606291596</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001425730995833874</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.209934140806261</v>
+        <v>3.176335827994847</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0008290139958262444</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.209934201431064</v>
+        <v>3.17633588861965</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.001120052300393581</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.209934072603357</v>
+        <v>3.176335759791943</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.003674347884953022</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.209934209009165</v>
+        <v>3.176335896197751</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.000535924918949604</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.209934383305473</v>
+        <v>3.17633607049406</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0006345035508275032</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.209934527289381</v>
+        <v>3.176336214477967</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.001141655258834362</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.209934360571172</v>
+        <v>3.176336047759759</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.001190387643873692</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.209934352993072</v>
+        <v>3.176336040181658</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.001041597686707973</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.209934065025257</v>
+        <v>3.176335752213843</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.001139259897172451</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.209934080181458</v>
+        <v>3.176335767370044</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0006808536127209663</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.20993430752447</v>
+        <v>3.176335994713056</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.001270999200642109</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.209934292368269</v>
+        <v>3.176335979556855</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.000273936428129673</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.209934398461674</v>
+        <v>3.176336085650261</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0009073996916413307</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.20993412565006</v>
+        <v>3.176335812838647</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.0009589912369847298</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.209934224165365</v>
+        <v>3.176335911353952</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.0006700986996293068</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.209934375727373</v>
+        <v>3.17633606291596</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0006228135898709297</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.209934390883574</v>
+        <v>3.17633607807216</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.000885319896042347</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.209934368149273</v>
+        <v>3.176336055337859</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.001072005368769169</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.209934451508377</v>
+        <v>3.176336138696963</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.0002929652109742165</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.209934550023682</v>
+        <v>3.176336237212269</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.0005474789068102837</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.209934383305473</v>
+        <v>3.17633607049406</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0007365988567471504</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1755625722227216</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.209934368149273</v>
+        <v>3.176336055337859</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.0009125685319304466</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.209934337836871</v>
+        <v>3.176336025025458</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0008980529382824898</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.209934322680671</v>
+        <v>3.176336009869257</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.0007186094298958778</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.209934360571172</v>
+        <v>3.176336047759759</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001084248535335064</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.209934375727373</v>
+        <v>3.17633606291596</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.001916888169944286</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.1755625722227216</v>
+        <v>0.72</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.209934368149273</v>
+        <v>3.176336055337859</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_1_000007.xlsx
+++ b/out/Attention-Mamba1_repeat_1_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.003990591503679752</v>
+        <v>0.003990593366324902</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.1599999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.004284373484551907</v>
+        <v>0.004284380935132504</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.01999999999999991</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.004108828492462635</v>
+        <v>0.004108822904527187</v>
       </c>
       <c r="JB4" t="n">
         <v>0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.007315183989703655</v>
+        <v>0.007315238006412983</v>
       </c>
       <c r="JB5" t="n">
         <v>0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.005404793657362461</v>
+        <v>0.005404791794717312</v>
       </c>
       <c r="JB6" t="n">
         <v>0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.0047961650416255</v>
+        <v>0.004796178080141544</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.004489299841225147</v>
+        <v>0.004489314742386341</v>
       </c>
       <c r="JB8" t="n">
         <v>0.8599999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.00481883343309164</v>
+        <v>0.004818824119865894</v>
       </c>
       <c r="JB9" t="n">
         <v>0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.004850310273468494</v>
+        <v>0.004850289784371853</v>
       </c>
       <c r="JB10" t="n">
         <v>0.5799999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.004848829470574856</v>
+        <v>0.004848849959671497</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.02000000000000007</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.004796112887561321</v>
+        <v>0.004796109162271023</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.02000000000000007</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.004667091183364391</v>
+        <v>0.004667087458074093</v>
       </c>
       <c r="JB13" t="n">
         <v>0.1199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.005218899808824062</v>
+        <v>0.005218916572630405</v>
       </c>
       <c r="JB14" t="n">
         <v>0.2599999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.004997228272259235</v>
+        <v>0.004997271113097668</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.005640235729515553</v>
+        <v>0.005640243180096149</v>
       </c>
       <c r="JB16" t="n">
         <v>0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.005384205840528011</v>
+        <v>0.005384194664657116</v>
       </c>
       <c r="JB17" t="n">
         <v>0.9999999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.005609533749520779</v>
+        <v>0.005609580315649509</v>
       </c>
       <c r="JB18" t="n">
         <v>0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.005334624089300632</v>
+        <v>0.005334620364010334</v>
       </c>
       <c r="JB19" t="n">
         <v>0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.005947175435721874</v>
+        <v>0.005947179161012173</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.006026570685207844</v>
+        <v>0.006026550196111202</v>
       </c>
       <c r="JB21" t="n">
         <v>0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.006300834007561207</v>
+        <v>0.006300837732851505</v>
       </c>
       <c r="JB22" t="n">
         <v>0.8599999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.007168627344071865</v>
+        <v>0.007168653421103954</v>
       </c>
       <c r="JB23" t="n">
         <v>0.1199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.005295452661812305</v>
+        <v>0.005295458249747753</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.005055048502981663</v>
+        <v>0.005055070854723454</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.004908098839223385</v>
+        <v>0.004908096976578236</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.004728215746581554</v>
+        <v>0.004728241823613644</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.004546920768916607</v>
+        <v>0.004546911455690861</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.8599999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.005342043004930019</v>
+        <v>0.005342052318155766</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.00474464800208807</v>
+        <v>0.00474462378770113</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.8599999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.004617695696651936</v>
+        <v>0.004617703147232533</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.8599999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.004413398914039135</v>
+        <v>0.004413395188748837</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.004430235363543034</v>
+        <v>0.004430231638252735</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.004700659774243832</v>
+        <v>0.004700672812759876</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.004757883958518505</v>
+        <v>0.004757874645292759</v>
       </c>
       <c r="JB35" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.006342954002320766</v>
+        <v>0.006342959590256214</v>
       </c>
       <c r="JB36" t="n">
         <v>0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.01323719788342714</v>
+        <v>0.0132371811196208</v>
       </c>
       <c r="JB37" t="n">
         <v>0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.005814737640321255</v>
+        <v>0.005814746953547001</v>
       </c>
       <c r="JB38" t="n">
         <v>0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.005190092138946056</v>
+        <v>0.00519010704010725</v>
       </c>
       <c r="JB39" t="n">
         <v>0.16</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.004678425379097462</v>
+        <v>0.004678403027355671</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.1199999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.004536076448857784</v>
+        <v>0.004536083899438381</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.003945988602936268</v>
+        <v>0.003946014679968357</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.006718714721500874</v>
+        <v>0.00671869982033968</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.16</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.007770820520818233</v>
+        <v>0.007770811207592487</v>
       </c>
       <c r="JB44" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.009559034369885921</v>
+        <v>0.009559019468724728</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.01067945081740618</v>
+        <v>0.01067943405359983</v>
       </c>
       <c r="JB46" t="n">
         <v>0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.001520373858511448</v>
+        <v>-0.001520386897027493</v>
       </c>
       <c r="JB47" t="n">
         <v>0.16</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.003825013525784016</v>
+        <v>0.00382502842694521</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.0009698392823338509</v>
+        <v>0.0009697778150439262</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.002762214280664921</v>
+        <v>0.002762197516858578</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.001154757104814053</v>
+        <v>0.001154777593910694</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.002791755832731724</v>
+        <v>0.00279174093157053</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.002511917613446712</v>
+        <v>0.002511919476091862</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.001991207711398602</v>
+        <v>0.001991203986108303</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.001991298981010914</v>
+        <v>0.001991336233913898</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.002091548405587673</v>
+        <v>0.002091567032039165</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.001099447719752789</v>
+        <v>0.001099466346204281</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.1199999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.01789640262722969</v>
+        <v>0.01789641752839088</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.1199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.002635910175740719</v>
+        <v>0.002635921351611614</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.1199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.0002836054190993309</v>
+        <v>0.0002835849300026894</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.1199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.001059277914464474</v>
+        <v>0.001059249974787235</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.3999999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.001585361547768116</v>
+        <v>0.001585367135703564</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.00221563596278429</v>
+        <v>0.002215641550719738</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.004041283391416073</v>
+        <v>0.00404129084199667</v>
       </c>
       <c r="JB64" t="n">
         <v>0.16</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.01334490161389112</v>
+        <v>0.01334490720182657</v>
       </c>
       <c r="JB65" t="n">
         <v>0.1600000000000001</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.04927634820342064</v>
+        <v>0.04927634447813034</v>
       </c>
       <c r="JB66" t="n">
         <v>0.1600000000000001</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.005197684280574322</v>
+        <v>-0.005197693593800068</v>
       </c>
       <c r="JB67" t="n">
         <v>0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.006580931134521961</v>
+        <v>-0.006580944173038006</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003174777142703533</v>
+        <v>-0.003174782730638981</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0003487290814518929</v>
+        <v>-0.0003487048670649529</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0001447601243853569</v>
+        <v>-0.0001447675749659538</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.0004219124093651772</v>
+        <v>0.0004219105467200279</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.001027452759444714</v>
+        <v>0.001027508638799191</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.001288971863687038</v>
+        <v>0.001288964413106441</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.001307575963437557</v>
+        <v>0.001307590864598751</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.001174743287265301</v>
+        <v>0.001174784265458584</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.000516415573656559</v>
+        <v>0.0005164248868823051</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.2599999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>3.176336055337859</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.001243737526237965</v>
+        <v>0.001243776641786098</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>3.176336055337859</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.002239192835986614</v>
+        <v>0.002239213325083256</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>3.176335873463449</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.002243299968540668</v>
+        <v>0.002243294380605221</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>3.176336040181658</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.0006087804213166237</v>
+        <v>0.0006087524816393852</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>3.176336237212269</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.0005947249010205269</v>
+        <v>0.0005947081372141838</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>3.17633607807216</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.001979992724955082</v>
+        <v>0.001979944296181202</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>3.176336115962662</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.002702820114791393</v>
+        <v>0.002702814526855946</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>3.176336312993273</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0006689475849270821</v>
+        <v>0.000668955035507679</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
         <v>3.176336290258972</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.0005878666415810585</v>
+        <v>0.0005878964439034462</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>3.176336138696963</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.0008665574714541435</v>
+        <v>0.0008665630593895912</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>3.17633606291596</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.001073666848242283</v>
+        <v>0.001073687337338924</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>3.176336161431264</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.002684065140783787</v>
+        <v>0.00268403347581625</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>3.176336169009365</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.001199589110910892</v>
+        <v>0.001199583522975445</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC90" t="n">
         <v>3.176336434242879</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.0008982056751847267</v>
+        <v>0.0008981982246041298</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>3.176336138696963</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.001836971379816532</v>
+        <v>0.001836995594203472</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>3.176336381196176</v>
@@ -74879,7 +74879,7 @@
         <v>0.000426863320171833</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>3.17633646455528</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.006517895497381687</v>
+        <v>0.006517884321510792</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>3.176336297837071</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.0006118053570389748</v>
+        <v>0.0006117904558777809</v>
       </c>
       <c r="JB95" t="n">
         <v>0.16</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.0008507268503308296</v>
+        <v>0.000850738026201725</v>
       </c>
       <c r="JB96" t="n">
         <v>0.16</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.0006534485146403313</v>
+        <v>0.0006534373387694359</v>
       </c>
       <c r="JB97" t="n">
         <v>0.02000000000000007</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.0008183671161532402</v>
+        <v>0.0008183503523468971</v>
       </c>
       <c r="JB98" t="n">
         <v>0.16</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.00131609383970499</v>
+        <v>0.001316091977059841</v>
       </c>
       <c r="JB99" t="n">
         <v>0.02000000000000007</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.001425730995833874</v>
+        <v>0.001425747759640217</v>
       </c>
       <c r="JB100" t="n">
         <v>0.02000000000000007</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.0008290139958262444</v>
+        <v>0.0008290307596325874</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.001120052300393581</v>
+        <v>0.001120061613619328</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.003674347884953022</v>
+        <v>0.003674332983791828</v>
       </c>
       <c r="JB103" t="n">
         <v>0.02000000000000007</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.000535924918949604</v>
+        <v>0.0005359435454010963</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.5799999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0006345035508275032</v>
+        <v>0.0006344998255372047</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.001141655258834362</v>
+        <v>0.00114165898412466</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.8599999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.001190387643873692</v>
+        <v>0.001190385781228542</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.001041597686707973</v>
+        <v>0.001041593961417675</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.001139259897172451</v>
+        <v>0.001139252446591854</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.5799999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0006808536127209663</v>
+        <v>0.000680859200656414</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.001270999200642109</v>
+        <v>0.001270982436835766</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.000273936428129673</v>
+        <v>0.0002739327028393745</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.8599999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.0009073996916413307</v>
+        <v>0.000907394103705883</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.8599999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.0009589912369847298</v>
+        <v>0.0009589577093720436</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.0006700986996293068</v>
+        <v>0.0006700875237584114</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.0006228135898709297</v>
+        <v>0.0006228284910321236</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.000885319896042347</v>
+        <v>0.0008853534236550331</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.001072005368769169</v>
+        <v>0.001071988604962826</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.8599999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.0002929652109742165</v>
+        <v>0.0002929782494902611</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.0005474789068102837</v>
+        <v>0.0005474714562296867</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.1199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.0007365988567471504</v>
+        <v>0.000736587680876255</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.0009125685319304466</v>
+        <v>0.0009125610813498497</v>
       </c>
       <c r="JB122" t="n">
         <v>0.02000000000000007</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.0008980529382824898</v>
+        <v>0.0008980398997664452</v>
       </c>
       <c r="JB123" t="n">
         <v>0.16</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.0007186094298958778</v>
+        <v>0.0007185926660895348</v>
       </c>
       <c r="JB124" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.001084248535335064</v>
+        <v>0.001084259711205959</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5800000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.001916888169944286</v>
+        <v>0.001916863955557346</v>
       </c>
       <c r="JB126" t="n">
         <v>0.72</v>
